--- a/Backtest/01-11-19/S&P500stock_01-11-19period252RS90.xlsx
+++ b/Backtest/01-11-19/S&P500stock_01-11-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>Stock</t>
   </si>
@@ -127,127 +127,70 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>ETR</t>
-  </si>
-  <si>
-    <t>ACGL</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>EW</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>ANSS</t>
-  </si>
-  <si>
-    <t>EQIX</t>
-  </si>
-  <si>
-    <t>AZO</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>MV</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-01-30</t>
-  </si>
-  <si>
-    <t>2020-01-22</t>
-  </si>
-  <si>
-    <t>2019-11-20</t>
-  </si>
-  <si>
-    <t>2019-11-06</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>Technology</t>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>ORLY</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>2019-02-21</t>
+  </si>
+  <si>
+    <t>2019-02-06</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
+  </si>
+  <si>
+    <t>2019-02-19</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>2019-02-27</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Utilities</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Scientific &amp; Technical Instruments</t>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
   </si>
   <si>
     <t>Utilities - Regulated Electric</t>
   </si>
   <si>
-    <t>Insurance - Diversified</t>
-  </si>
-  <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Software - Application</t>
-  </si>
-  <si>
-    <t>REIT - Specialty</t>
+    <t>Utilities - Independent Power Producers</t>
   </si>
   <si>
     <t>Specialty Retail</t>
   </si>
   <si>
-    <t>Building Products &amp; Equipment</t>
+    <t>Utilities - Diversified</t>
   </si>
 </sst>
 </file>
@@ -605,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -726,40 +669,40 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>98.57433808553971</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="D2">
-        <v>100.91</v>
+        <v>35.47</v>
       </c>
       <c r="E2">
-        <v>2.22</v>
+        <v>4.08</v>
       </c>
       <c r="F2">
-        <v>1.667373767888238</v>
+        <v>1.042297874363037</v>
       </c>
       <c r="G2">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="H2">
-        <v>2.309846792976287</v>
+        <v>1.465260281238622</v>
       </c>
       <c r="I2">
-        <v>102.4580001831055</v>
+        <v>32.91799964904785</v>
       </c>
       <c r="J2">
-        <v>98.71350059509277</v>
+        <v>29.93287496566773</v>
       </c>
       <c r="K2">
-        <v>98.1300001525879</v>
+        <v>31.66394992828369</v>
       </c>
       <c r="L2">
-        <v>87.77125022888184</v>
+        <v>27.92037497520447</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>1.04</v>
@@ -783,52 +726,52 @@
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>53.21</v>
+        <v>13.23</v>
       </c>
       <c r="Y2">
-        <v>104.54</v>
+        <v>38.03</v>
       </c>
       <c r="Z2">
-        <v>17.1</v>
+        <v>12.92</v>
       </c>
       <c r="AA2">
-        <v>6.1</v>
+        <v>-134.43</v>
       </c>
       <c r="AB2">
-        <v>165.08</v>
+        <v>173.13</v>
       </c>
       <c r="AC2">
-        <v>241.67</v>
+        <v>630</v>
       </c>
       <c r="AD2">
-        <v>5.41</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE2">
-        <v>4.94</v>
+        <v>55.88</v>
       </c>
       <c r="AF2">
-        <v>32.79</v>
+        <v>221.43</v>
       </c>
       <c r="AG2">
-        <v>201.67</v>
+        <v>-180</v>
       </c>
       <c r="AH2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="AK2">
-        <v>76.71768635932708</v>
+        <v>89.21436771595779</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -836,43 +779,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>90.22403258655804</v>
+        <v>92.98969072164948</v>
       </c>
       <c r="C3">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="D3">
-        <v>60.74</v>
+        <v>35.95</v>
       </c>
       <c r="E3">
-        <v>0.97</v>
+        <v>2.86</v>
       </c>
       <c r="F3">
-        <v>-0.8999710594872684</v>
+        <v>-0.01110139747842291</v>
       </c>
       <c r="G3">
-        <v>0.82</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
-        <v>-1.524608963433911</v>
+        <v>-0.009091583958047636</v>
       </c>
       <c r="I3">
-        <v>60.04700012207032</v>
+        <v>35.16800003051758</v>
       </c>
       <c r="J3">
-        <v>59.29225025177002</v>
+        <v>34.5709997177124</v>
       </c>
       <c r="K3">
-        <v>58.03829986572266</v>
+        <v>35.69379981994629</v>
       </c>
       <c r="L3">
-        <v>51.09829998016357</v>
+        <v>33.69920003890991</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -890,7 +833,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -899,46 +842,46 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>40.51</v>
+        <v>25.04</v>
       </c>
       <c r="Y3">
-        <v>60.88</v>
+        <v>39.44</v>
       </c>
       <c r="Z3">
-        <v>11.76</v>
+        <v>54.05</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>-1959.18</v>
       </c>
       <c r="AB3">
-        <v>100.5</v>
+        <v>182.35</v>
       </c>
       <c r="AC3">
-        <v>597.3</v>
+        <v>168.89</v>
       </c>
       <c r="AD3">
-        <v>3.68</v>
+        <v>5.21</v>
       </c>
       <c r="AE3">
-        <v>50.82</v>
+        <v>-22.5</v>
       </c>
       <c r="AF3">
-        <v>-8.960000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AG3">
-        <v>462.16</v>
+        <v>148.89</v>
       </c>
       <c r="AH3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" t="s">
         <v>50</v>
       </c>
-      <c r="AI3" t="s">
-        <v>61</v>
-      </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="AK3">
-        <v>75.96534214479246</v>
+        <v>85.04752842427665</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -946,43 +889,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>93.07535641547861</v>
+        <v>98.55670103092784</v>
       </c>
       <c r="C4">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D4">
-        <v>41.76</v>
+        <v>133.04</v>
       </c>
       <c r="E4">
-        <v>1.21</v>
+        <v>4.77</v>
       </c>
       <c r="F4">
-        <v>-0.4070408526311712</v>
+        <v>1.638072872371731</v>
       </c>
       <c r="G4">
-        <v>1.12</v>
+        <v>3.66</v>
       </c>
       <c r="H4">
-        <v>-0.9191685808428265</v>
+        <v>1.263730170168573</v>
       </c>
       <c r="I4">
-        <v>41.25999908447265</v>
+        <v>123.8699981689453</v>
       </c>
       <c r="J4">
-        <v>41.54300003051758</v>
+        <v>120.0979995727539</v>
       </c>
       <c r="K4">
-        <v>41.02180000305176</v>
+        <v>126.1186001586914</v>
       </c>
       <c r="L4">
-        <v>35.94509991645813</v>
+        <v>114.762149848938</v>
       </c>
       <c r="M4">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1000,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1009,46 +952,46 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>24.79</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="Y4">
-        <v>42.86</v>
+        <v>154.06</v>
       </c>
       <c r="Z4">
-        <v>17.35</v>
+        <v>10.1</v>
       </c>
       <c r="AA4">
-        <v>11.47</v>
+        <v>24.96</v>
       </c>
       <c r="AB4">
-        <v>53.98</v>
+        <v>136.76</v>
       </c>
       <c r="AC4">
-        <v>216.67</v>
+        <v>169.25</v>
       </c>
       <c r="AD4">
-        <v>3.55</v>
+        <v>12.62</v>
       </c>
       <c r="AE4">
-        <v>-16.67</v>
+        <v>-2.13</v>
       </c>
       <c r="AF4">
-        <v>4.59</v>
+        <v>83.8</v>
       </c>
       <c r="AG4">
-        <v>263.33</v>
+        <v>138.49</v>
       </c>
       <c r="AH4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="AK4">
-        <v>60.59396786371079</v>
+        <v>70.71850161804439</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1056,64 +999,61 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>91.85336048879837</v>
+        <v>92.78350515463917</v>
       </c>
       <c r="C5">
-        <v>221</v>
+        <v>124</v>
       </c>
       <c r="D5">
-        <v>58.03</v>
+        <v>38.58</v>
       </c>
       <c r="E5">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="F5">
-        <v>-0.07842071472710618</v>
+        <v>-1.099038350363865</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="H5">
-        <v>0.4531629530302966</v>
+        <v>-1.228879098329392</v>
       </c>
       <c r="I5">
-        <v>57.70399932861328</v>
+        <v>37.90400009155273</v>
       </c>
       <c r="J5">
-        <v>55.17349987030029</v>
+        <v>37.61599979400635</v>
       </c>
       <c r="K5">
-        <v>53.56559997558594</v>
+        <v>37.8841999053955</v>
       </c>
       <c r="L5">
-        <v>48.02794994354248</v>
+        <v>36.23379997253418</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.08</v>
-      </c>
-      <c r="O5" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>7.222222222222221</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -1122,46 +1062,46 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>35.38</v>
+        <v>29.34</v>
       </c>
       <c r="Y5">
-        <v>58.14</v>
+        <v>39.88</v>
       </c>
       <c r="Z5">
-        <v>13.43</v>
+        <v>18.77</v>
       </c>
       <c r="AA5">
-        <v>4.2</v>
+        <v>-218.9</v>
       </c>
       <c r="AB5">
-        <v>25.75</v>
+        <v>78.2</v>
       </c>
       <c r="AC5">
-        <v>124.2</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="AD5">
-        <v>45.47</v>
+        <v>5.87</v>
       </c>
       <c r="AE5">
-        <v>410.14</v>
+        <v>-464.29</v>
       </c>
       <c r="AF5">
-        <v>-48.89</v>
+        <v>-89.02</v>
       </c>
       <c r="AG5">
-        <v>-14.01</v>
+        <v>145.37</v>
       </c>
       <c r="AH5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AI5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>57.60590650503779</v>
+        <v>54.08245888969593</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1169,43 +1109,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>97.14867617107943</v>
+        <v>97.11340206185567</v>
       </c>
       <c r="C6">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D6">
-        <v>79.45999999999999</v>
+        <v>40.41</v>
       </c>
       <c r="E6">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="F6">
-        <v>0.6815133541760433</v>
+        <v>-0.287402845830281</v>
       </c>
       <c r="G6">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="H6">
-        <v>0.130261415648385</v>
+        <v>-0.4439723499513099</v>
       </c>
       <c r="I6">
-        <v>78.76466674804688</v>
+        <v>39.68000030517578</v>
       </c>
       <c r="J6">
-        <v>76.20449981689453</v>
+        <v>39.50349998474121</v>
       </c>
       <c r="K6">
-        <v>74.22033340454101</v>
+        <v>38.98400001525879</v>
       </c>
       <c r="L6">
-        <v>64.8513166809082</v>
+        <v>34.78865002632141</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1232,46 +1172,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>46.55</v>
+        <v>23.75</v>
       </c>
       <c r="Y6">
-        <v>80.52</v>
+        <v>43.08</v>
       </c>
       <c r="Z6">
-        <v>46.64</v>
+        <v>11.18</v>
       </c>
       <c r="AA6">
-        <v>12.93</v>
+        <v>3520</v>
       </c>
       <c r="AB6">
-        <v>8.42</v>
+        <v>60.04</v>
       </c>
       <c r="AC6">
-        <v>3208.27</v>
+        <v>95.03</v>
       </c>
       <c r="AD6">
-        <v>7.2</v>
+        <v>-30.66</v>
       </c>
       <c r="AE6">
-        <v>12.82</v>
+        <v>-204.35</v>
       </c>
       <c r="AF6">
-        <v>-2.5</v>
+        <v>-73.86</v>
       </c>
       <c r="AG6">
-        <v>2907.52</v>
+        <v>118.22</v>
       </c>
       <c r="AH6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="AI6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AJ6" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="AK6">
-        <v>49.59811931603053</v>
+        <v>51.79892256390887</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1279,109 +1219,109 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.98167006109979</v>
+        <v>94.63917525773195</v>
       </c>
       <c r="C7">
-        <v>261</v>
+        <v>410</v>
       </c>
       <c r="D7">
-        <v>61.22</v>
+        <v>343.44</v>
       </c>
       <c r="E7">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="F7">
-        <v>1.27713735412716</v>
+        <v>-0.8831778438389752</v>
       </c>
       <c r="G7">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="H7">
-        <v>0.4935256452030356</v>
+        <v>-0.5394339815108063</v>
       </c>
       <c r="I7">
-        <v>63.05799942016601</v>
+        <v>340.9120056152344</v>
       </c>
       <c r="J7">
-        <v>60.91999988555908</v>
+        <v>341.9150039672851</v>
       </c>
       <c r="K7">
-        <v>58.14060012817383</v>
+        <v>342.6464007568359</v>
       </c>
       <c r="L7">
-        <v>47.87080005645752</v>
+        <v>307.1354512023926</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
         <v>1</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>28.73</v>
+        <v>217.64</v>
       </c>
       <c r="Y7">
-        <v>65.44</v>
+        <v>363.2</v>
       </c>
       <c r="Z7">
-        <v>10.45</v>
+        <v>28.28</v>
       </c>
       <c r="AA7">
-        <v>205.62</v>
+        <v>6.02</v>
       </c>
       <c r="AB7">
-        <v>47.87</v>
+        <v>3.95</v>
       </c>
       <c r="AC7">
-        <v>2.56</v>
+        <v>28.25</v>
       </c>
       <c r="AD7">
-        <v>9.16</v>
+        <v>73.47</v>
       </c>
       <c r="AE7">
-        <v>40.35</v>
+        <v>5.09</v>
       </c>
       <c r="AF7">
-        <v>-9.52</v>
+        <v>18.36</v>
       </c>
       <c r="AG7">
-        <v>-19.23</v>
+        <v>3.11</v>
       </c>
       <c r="AH7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="AI7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="AK7">
-        <v>39.31541157899333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1389,43 +1329,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>98.37067209775967</v>
+        <v>97.52577319587628</v>
       </c>
       <c r="C8">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D8">
-        <v>20.66</v>
+        <v>15.34</v>
       </c>
       <c r="E8">
-        <v>0.9</v>
+        <v>2.41</v>
       </c>
       <c r="F8">
-        <v>-1.043742369820297</v>
+        <v>-0.3996503092232233</v>
       </c>
       <c r="G8">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="H8">
-        <v>-0.3540908904244821</v>
+        <v>-0.5076134376576408</v>
       </c>
       <c r="I8">
-        <v>20.9620002746582</v>
+        <v>14.95200023651123</v>
       </c>
       <c r="J8">
-        <v>20.55762500762939</v>
+        <v>14.77950000762939</v>
       </c>
       <c r="K8">
-        <v>20.1142000579834</v>
+        <v>15.09560001373291</v>
       </c>
       <c r="L8">
-        <v>17.43228754043579</v>
+        <v>13.59494999408722</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1443,495 +1383,55 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
         <v>1</v>
-      </c>
-      <c r="V8" t="b">
-        <v>0</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
       </c>
       <c r="X8">
-        <v>11.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Y8">
-        <v>21.33</v>
+        <v>16.28</v>
       </c>
       <c r="Z8">
-        <v>18.64</v>
+        <v>9.31</v>
       </c>
       <c r="AA8">
-        <v>242.91</v>
+        <v>-47.59</v>
       </c>
       <c r="AB8">
-        <v>12.23</v>
+        <v>87.5</v>
       </c>
       <c r="AC8">
-        <v>34.69</v>
+        <v>107.39</v>
       </c>
       <c r="AD8">
-        <v>8.630000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="AE8">
-        <v>-22.35</v>
+        <v>-65.91</v>
       </c>
       <c r="AF8">
-        <v>49.12</v>
+        <v>-57.69</v>
       </c>
       <c r="AG8">
-        <v>16.33</v>
+        <v>151.23</v>
       </c>
       <c r="AH8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AI8" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="AJ8" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="AK8">
-        <v>31.23760841504848</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>92.4643584521385</v>
-      </c>
-      <c r="C9">
-        <v>470</v>
-      </c>
-      <c r="D9">
-        <v>220.15</v>
-      </c>
-      <c r="E9">
-        <v>1.56</v>
-      </c>
-      <c r="F9">
-        <v>0.3118156990339706</v>
-      </c>
-      <c r="G9">
-        <v>1.81</v>
-      </c>
-      <c r="H9">
-        <v>0.4733442991166661</v>
-      </c>
-      <c r="I9">
-        <v>222.3040008544922</v>
-      </c>
-      <c r="J9">
-        <v>221.2740005493164</v>
-      </c>
-      <c r="K9">
-        <v>217.0438003540039</v>
-      </c>
-      <c r="L9">
-        <v>196.1660998535156</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1.02</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" t="b">
-        <v>1</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>136.8</v>
-      </c>
-      <c r="Y9">
-        <v>229.2</v>
-      </c>
-      <c r="Z9">
-        <v>17.51</v>
-      </c>
-      <c r="AA9">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="AB9">
-        <v>12.47</v>
-      </c>
-      <c r="AC9">
-        <v>23.58</v>
-      </c>
-      <c r="AD9">
-        <v>3.9</v>
-      </c>
-      <c r="AE9">
-        <v>27.18</v>
-      </c>
-      <c r="AF9">
-        <v>-43.72</v>
-      </c>
-      <c r="AG9">
-        <v>72.64</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK9">
-        <v>29.57233105133433</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10">
-        <v>92.26069246435846</v>
-      </c>
-      <c r="C10">
-        <v>457</v>
-      </c>
-      <c r="D10">
-        <v>566.78</v>
-      </c>
-      <c r="E10">
-        <v>0.77</v>
-      </c>
-      <c r="F10">
-        <v>-1.310746231867349</v>
-      </c>
-      <c r="G10">
-        <v>1.23</v>
-      </c>
-      <c r="H10">
-        <v>-0.6971737738927627</v>
-      </c>
-      <c r="I10">
-        <v>567.6660034179688</v>
-      </c>
-      <c r="J10">
-        <v>570.6565032958985</v>
-      </c>
-      <c r="K10">
-        <v>563.7116027832031</v>
-      </c>
-      <c r="L10">
-        <v>492.8369006347656</v>
-      </c>
-      <c r="M10">
-        <v>0.99</v>
-      </c>
-      <c r="N10">
-        <v>1.01</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0.5555555555555555</v>
-      </c>
-      <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>335.29</v>
-      </c>
-      <c r="Y10">
-        <v>609.97</v>
-      </c>
-      <c r="Z10">
-        <v>49.36</v>
-      </c>
-      <c r="AA10">
-        <v>-7.24</v>
-      </c>
-      <c r="AB10">
-        <v>9.59</v>
-      </c>
-      <c r="AC10">
-        <v>2.9</v>
-      </c>
-      <c r="AD10">
-        <v>1.38</v>
-      </c>
-      <c r="AE10">
-        <v>-16.47</v>
-      </c>
-      <c r="AF10">
-        <v>18.06</v>
-      </c>
-      <c r="AG10">
-        <v>4.35</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK10">
-        <v>17.4848776157103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11">
-        <v>93.48268839103869</v>
-      </c>
-      <c r="C11">
-        <v>487</v>
-      </c>
-      <c r="D11">
-        <v>1144.38</v>
-      </c>
-      <c r="E11">
-        <v>0.98</v>
-      </c>
-      <c r="F11">
-        <v>-0.8794323008682643</v>
-      </c>
-      <c r="G11">
-        <v>1.36</v>
-      </c>
-      <c r="H11">
-        <v>-0.4348162747699595</v>
-      </c>
-      <c r="I11">
-        <v>1143.552001953125</v>
-      </c>
-      <c r="J11">
-        <v>1102.530499267578</v>
-      </c>
-      <c r="K11">
-        <v>1108.176398925781</v>
-      </c>
-      <c r="L11">
-        <v>1044.578399963379</v>
-      </c>
-      <c r="M11">
-        <v>1.04</v>
-      </c>
-      <c r="N11">
-        <v>1.03</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="b">
-        <v>1</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>731.17</v>
-      </c>
-      <c r="Y11">
-        <v>1186.6</v>
-      </c>
-      <c r="Z11">
-        <v>28.09</v>
-      </c>
-      <c r="AA11">
-        <v>0.83</v>
-      </c>
-      <c r="AB11">
-        <v>2.34</v>
-      </c>
-      <c r="AC11">
-        <v>67.83</v>
-      </c>
-      <c r="AD11">
-        <v>-32.98</v>
-      </c>
-      <c r="AE11">
-        <v>40.73</v>
-      </c>
-      <c r="AF11">
-        <v>39.62</v>
-      </c>
-      <c r="AG11">
-        <v>-14.59</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK11">
-        <v>15.23591825671734</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12">
-        <v>98.77800407331976</v>
-      </c>
-      <c r="C12">
-        <v>366</v>
-      </c>
-      <c r="D12">
-        <v>22.61</v>
-      </c>
-      <c r="E12">
-        <v>1.74</v>
-      </c>
-      <c r="F12">
-        <v>0.6815133541760433</v>
-      </c>
-      <c r="G12">
-        <v>1.61</v>
-      </c>
-      <c r="H12">
-        <v>0.06971737738927698</v>
-      </c>
-      <c r="I12">
-        <v>22.72000045776367</v>
-      </c>
-      <c r="J12">
-        <v>21.95200004577637</v>
-      </c>
-      <c r="K12">
-        <v>20.6946000289917</v>
-      </c>
-      <c r="L12">
-        <v>16.51125003814697</v>
-      </c>
-      <c r="M12">
-        <v>1.03</v>
-      </c>
-      <c r="N12">
-        <v>1.1</v>
-      </c>
-      <c r="P12">
-        <v>2</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>4.444444444444444</v>
-      </c>
-      <c r="U12" t="b">
-        <v>1</v>
-      </c>
-      <c r="V12" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-      <c r="X12">
-        <v>10.15</v>
-      </c>
-      <c r="Y12">
-        <v>23.5</v>
-      </c>
-      <c r="Z12">
-        <v>2.41</v>
-      </c>
-      <c r="AA12">
-        <v>704.86</v>
-      </c>
-      <c r="AB12">
-        <v>43.97</v>
-      </c>
-      <c r="AC12">
-        <v>47.83</v>
-      </c>
-      <c r="AD12">
-        <v>10.03</v>
-      </c>
-      <c r="AE12">
-        <v>17.24</v>
-      </c>
-      <c r="AF12">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="AG12">
-        <v>-32.61</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK12">
-        <v>56.22987210820462</v>
+        <v>58.83503273648435</v>
       </c>
     </row>
   </sheetData>
